--- a/Tests/Validation/Wheat/data/FAR HYC W19-03-1.xlsx
+++ b/Tests/Validation/Wheat/data/FAR HYC W19-03-1.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,131 +430,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Seeds</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber.se</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation.se</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
@@ -553,36 +546,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>330.847229022101</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.171314346480023</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>330.847229022101</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.171314346480023</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -593,10 +572,6 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -604,36 +579,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>222.3125</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.11056848839068</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>222.3125</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.11056848839068</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -644,10 +605,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,34 +612,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D4" t="n">
+        <v>0.6225000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.6225000000000001</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.0265753645318366</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -695,10 +638,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -706,34 +645,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D5" t="n">
+        <v>0.855</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="I5" t="n">
         <v>0.00645497224367903</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -746,10 +671,6 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -757,50 +678,32 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>776.875</v>
+      </c>
+      <c r="K6" t="n">
+        <v>29.6397642534484</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>776.875</v>
-      </c>
-      <c r="O6" t="n">
-        <v>29.6397642534484</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -808,34 +711,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D7" t="n">
+        <v>0.8149999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="I7" t="n">
         <v>0.00499999999999997</v>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -848,10 +737,6 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -859,7 +744,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -867,60 +752,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>81.9405</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.22659269626358</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.202072594216369</v>
+      </c>
       <c r="P8" t="n">
-        <v>81.9405</v>
+        <v>9.975</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.22659269626358</v>
+        <v>0.165201896679992</v>
       </c>
       <c r="R8" t="n">
-        <v>12.45</v>
+        <v>1.11484891597776</v>
       </c>
       <c r="S8" t="n">
-        <v>0.202072594216369</v>
+        <v>0.111844021987392</v>
       </c>
       <c r="T8" t="n">
-        <v>9.975</v>
+        <v>922.356924308463</v>
       </c>
       <c r="U8" t="n">
-        <v>0.165201896679992</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.11484891597776</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.111844021987392</v>
-      </c>
-      <c r="X8" t="n">
-        <v>922.356924308463</v>
-      </c>
-      <c r="Y8" t="n">
         <v>0.178376491534519</v>
       </c>
     </row>
@@ -930,7 +797,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -938,38 +805,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
         <v>2585.35777665987</v>
       </c>
-      <c r="K9" t="n">
+      <c r="G9" t="n">
         <v>1.54413393527776</v>
       </c>
-      <c r="L9" t="n">
+      <c r="H9" t="n">
         <v>576.25</v>
       </c>
-      <c r="M9" t="n">
+      <c r="I9" t="n">
         <v>36.3074257785741</v>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -978,10 +831,6 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -989,36 +838,22 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>325.668084098099</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.239079339518042</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>325.668084098099</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.239079339518042</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1029,10 +864,6 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1040,36 +871,22 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>238.375</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.161007569697825</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>238.375</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.161007569697825</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1080,10 +897,6 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1091,34 +904,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D12" t="n">
+        <v>0.755</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="I12" t="n">
         <v>0.0184842275106824</v>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1131,10 +930,6 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1142,34 +937,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D13" t="n">
+        <v>0.8675</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8675</v>
-      </c>
-      <c r="I13" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1182,10 +963,6 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1193,50 +970,32 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>816.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>67.9192228557817</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>816.25</v>
-      </c>
-      <c r="O14" t="n">
-        <v>67.9192228557817</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1244,34 +1003,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D15" t="n">
+        <v>0.7775</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0.7775</v>
-      </c>
-      <c r="I15" t="n">
         <v>0.0103077640640442</v>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1284,10 +1029,6 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1295,7 +1036,7 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1303,60 +1044,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>81.806</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.206003236220534</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.14361406616345</v>
+      </c>
       <c r="P16" t="n">
-        <v>81.806</v>
+        <v>11.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.206003236220534</v>
+        <v>0.070710678118655</v>
       </c>
       <c r="R16" t="n">
-        <v>12.275</v>
+        <v>1.27191720816828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.14361406616345</v>
+        <v>0.0843368064412565</v>
       </c>
       <c r="T16" t="n">
-        <v>11.2</v>
+        <v>858.572915360606</v>
       </c>
       <c r="U16" t="n">
-        <v>0.070710678118655</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.27191720816828</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.0843368064412565</v>
-      </c>
-      <c r="X16" t="n">
-        <v>858.572915360606</v>
-      </c>
-      <c r="Y16" t="n">
         <v>0.334158836975862</v>
       </c>
     </row>
@@ -1366,7 +1089,7 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds100CvBennett</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1374,38 +1097,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
         <v>2672.05110785988</v>
       </c>
-      <c r="K17" t="n">
+      <c r="G17" t="n">
         <v>1.13383446749</v>
       </c>
-      <c r="L17" t="n">
+      <c r="H17" t="n">
         <v>518.75</v>
       </c>
-      <c r="M17" t="n">
+      <c r="I17" t="n">
         <v>33.2368395007708</v>
       </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1414,10 +1123,6 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1425,36 +1130,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>349.086694688289</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.258797374974961</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>349.086694688289</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.258797374974961</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -1465,10 +1156,6 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1476,36 +1163,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>218.25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.191273146747437</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>218.25</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.191273146747437</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1516,10 +1189,6 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1527,34 +1196,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D20" t="n">
+        <v>0.6425</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0.6425</v>
-      </c>
-      <c r="I20" t="n">
         <v>0.00750000000000002</v>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1567,10 +1222,6 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1578,34 +1229,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D21" t="n">
+        <v>0.85</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I21" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1618,10 +1255,6 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1629,50 +1262,32 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>725</v>
+      </c>
+      <c r="K22" t="n">
+        <v>24.3883510444365</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>725</v>
-      </c>
-      <c r="O22" t="n">
-        <v>24.3883510444365</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1680,34 +1295,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D23" t="n">
+        <v>0.8175</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0.8175</v>
-      </c>
-      <c r="I23" t="n">
         <v>0.00478713553878168</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1720,10 +1321,6 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1731,7 +1328,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1739,60 +1336,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>81.764</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.374518357360489</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.108012344973464</v>
+      </c>
       <c r="P24" t="n">
-        <v>81.764</v>
+        <v>10.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.374518357360489</v>
+        <v>0.122474487139159</v>
       </c>
       <c r="R24" t="n">
-        <v>12.3</v>
+        <v>1.19480357010161</v>
       </c>
       <c r="S24" t="n">
-        <v>0.108012344973464</v>
+        <v>0.21245489568302</v>
       </c>
       <c r="T24" t="n">
-        <v>10.4</v>
+        <v>891.553305097714</v>
       </c>
       <c r="U24" t="n">
-        <v>0.122474487139159</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.19480357010161</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.21245489568302</v>
-      </c>
-      <c r="X24" t="n">
-        <v>891.553305097714</v>
-      </c>
-      <c r="Y24" t="n">
         <v>0.190757822850093</v>
       </c>
     </row>
@@ -1802,7 +1381,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds100CvBennett</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1810,38 +1389,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
         <v>2509.67428780047</v>
       </c>
-      <c r="K25" t="n">
+      <c r="G25" t="n">
         <v>0.732084138486886</v>
       </c>
-      <c r="L25" t="n">
+      <c r="H25" t="n">
         <v>538.125</v>
       </c>
-      <c r="M25" t="n">
+      <c r="I25" t="n">
         <v>18.125</v>
       </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -1850,10 +1415,6 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1861,36 +1422,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>175</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>362.510315149272</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.178356781758447</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>362.510315149272</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.178356781758447</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -1901,10 +1448,6 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1912,36 +1455,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>175</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>245.625</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0278107443266087</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>245.625</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.0278107443266087</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -1952,10 +1481,6 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1963,34 +1488,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D28" t="n">
+        <v>0.65</v>
       </c>
       <c r="E28" t="n">
-        <v>175</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I28" t="n">
         <v>0.0234520787991172</v>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2003,10 +1514,6 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2014,34 +1521,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D29" t="n">
+        <v>0.85</v>
       </c>
       <c r="E29" t="n">
-        <v>175</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I29" t="n">
         <v>0.00816496580927727</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2054,10 +1547,6 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2065,50 +1554,32 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>175</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>836.25</v>
+      </c>
+      <c r="K30" t="n">
+        <v>24.7592575279093</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>836.25</v>
-      </c>
-      <c r="O30" t="n">
-        <v>24.7592575279093</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2116,34 +1587,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D31" t="n">
+        <v>0.8175</v>
       </c>
       <c r="E31" t="n">
-        <v>175</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>0.8175</v>
-      </c>
-      <c r="I31" t="n">
         <v>0.00478713553878166</v>
       </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2156,10 +1613,6 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2167,7 +1620,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -2175,60 +1628,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>175</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>81.90300000000001</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.126579355873433</v>
+      </c>
+      <c r="N32" t="n">
+        <v>12.275</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.174999999999999</v>
+      </c>
       <c r="P32" t="n">
-        <v>81.90300000000001</v>
+        <v>10.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.126579355873433</v>
+        <v>0.244948974278318</v>
       </c>
       <c r="R32" t="n">
-        <v>12.275</v>
+        <v>1.2653591655577</v>
       </c>
       <c r="S32" t="n">
-        <v>0.174999999999999</v>
+        <v>0.102652611891444</v>
       </c>
       <c r="T32" t="n">
-        <v>10.2</v>
+        <v>898.248195042972</v>
       </c>
       <c r="U32" t="n">
-        <v>0.244948974278318</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.2653591655577</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.102652611891444</v>
-      </c>
-      <c r="X32" t="n">
-        <v>898.248195042972</v>
-      </c>
-      <c r="Y32" t="n">
         <v>0.144457887421278</v>
       </c>
     </row>
@@ -2238,7 +1673,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -2246,38 +1681,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>175</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
         <v>2539.51520733229</v>
       </c>
-      <c r="K33" t="n">
+      <c r="G33" t="n">
         <v>0.200860898105909</v>
       </c>
-      <c r="L33" t="n">
+      <c r="H33" t="n">
         <v>597.5</v>
       </c>
-      <c r="M33" t="n">
+      <c r="I33" t="n">
         <v>13.6549746734783</v>
       </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
@@ -2286,10 +1707,6 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2297,36 +1714,22 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>175</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>346.426554931055</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.117082756744289</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>346.426554931055</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.117082756744289</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -2337,10 +1740,6 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2348,36 +1747,22 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>175</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.138898194132729</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>239.5</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.138898194132729</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -2388,10 +1773,6 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2399,34 +1780,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D36" t="n">
+        <v>0.7675</v>
       </c>
       <c r="E36" t="n">
-        <v>175</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>0.7675</v>
-      </c>
-      <c r="I36" t="n">
         <v>0.0160078105935821</v>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2439,10 +1806,6 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2450,34 +1813,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D37" t="n">
+        <v>0.8774999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>175</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>0.8774999999999999</v>
-      </c>
-      <c r="I37" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2490,10 +1839,6 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2501,50 +1846,32 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>175</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>796.25</v>
+      </c>
+      <c r="K38" t="n">
+        <v>28.75</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>796.25</v>
-      </c>
-      <c r="O38" t="n">
-        <v>28.75</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2552,34 +1879,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D39" t="n">
+        <v>0.795</v>
       </c>
       <c r="E39" t="n">
-        <v>175</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="I39" t="n">
         <v>0.00645497224367904</v>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2592,10 +1905,6 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2603,7 +1912,7 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -2611,60 +1920,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>175</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>81.11750000000001</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.700510468634599</v>
+      </c>
+      <c r="N40" t="n">
+        <v>12.325</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.08539125638299661</v>
+      </c>
       <c r="P40" t="n">
-        <v>81.11750000000001</v>
+        <v>11.125</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.700510468634599</v>
+        <v>0.165201896679992</v>
       </c>
       <c r="R40" t="n">
-        <v>12.325</v>
+        <v>1.18260841868301</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08539125638299661</v>
+        <v>0.108220304283074</v>
       </c>
       <c r="T40" t="n">
-        <v>11.125</v>
+        <v>830.646946406623</v>
       </c>
       <c r="U40" t="n">
-        <v>0.165201896679992</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.18260841868301</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.108220304283074</v>
-      </c>
-      <c r="X40" t="n">
-        <v>830.646946406623</v>
-      </c>
-      <c r="Y40" t="n">
         <v>0.268139224479565</v>
       </c>
     </row>
@@ -2674,7 +1965,7 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds175CvBennett</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2682,38 +1973,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>175</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
         <v>2393.13126004684</v>
       </c>
-      <c r="K41" t="n">
+      <c r="G41" t="n">
         <v>1.59394234088132</v>
       </c>
-      <c r="L41" t="n">
+      <c r="H41" t="n">
         <v>538.125</v>
       </c>
-      <c r="M41" t="n">
+      <c r="I41" t="n">
         <v>31.7440119025095</v>
       </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
@@ -2722,10 +1999,6 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2733,36 +2006,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>175</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>371.923072430279</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.102676785288704</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>371.923072430279</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.102676785288704</v>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -2773,10 +2032,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2784,36 +2039,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>175</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>224.0625</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0964601331725531</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>224.0625</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.0964601331725531</v>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -2824,10 +2065,6 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2835,34 +2072,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D44" t="n">
+        <v>0.64</v>
       </c>
       <c r="E44" t="n">
-        <v>175</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I44" t="n">
         <v>0.0108012344973464</v>
       </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2875,10 +2098,6 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2886,34 +2105,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D45" t="n">
+        <v>0.8475</v>
       </c>
       <c r="E45" t="n">
-        <v>175</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>0.8475</v>
-      </c>
-      <c r="I45" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2926,10 +2131,6 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2937,50 +2138,32 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>175</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>873.125</v>
+      </c>
+      <c r="K46" t="n">
+        <v>22.3926838870794</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>873.125</v>
-      </c>
-      <c r="O46" t="n">
-        <v>22.3926838870794</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2988,34 +2171,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D47" t="n">
+        <v>0.8149999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>175</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="I47" t="n">
         <v>0.00499999999999997</v>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -3028,10 +2197,6 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3039,7 +2204,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -3047,60 +2212,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>175</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>82.027</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.148841078559202</v>
+      </c>
+      <c r="N48" t="n">
+        <v>12.225</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.143614066163451</v>
+      </c>
       <c r="P48" t="n">
-        <v>82.027</v>
+        <v>10.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.148841078559202</v>
+        <v>0.147196014438797</v>
       </c>
       <c r="R48" t="n">
-        <v>12.225</v>
+        <v>1.22708118690709</v>
       </c>
       <c r="S48" t="n">
-        <v>0.143614066163451</v>
+        <v>0.124129586137575</v>
       </c>
       <c r="T48" t="n">
-        <v>10.3</v>
+        <v>907.115607419586</v>
       </c>
       <c r="U48" t="n">
-        <v>0.147196014438797</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.22708118690709</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.124129586137575</v>
-      </c>
-      <c r="X48" t="n">
-        <v>907.115607419586</v>
-      </c>
-      <c r="Y48" t="n">
         <v>0.14726961922209</v>
       </c>
     </row>
@@ -3110,7 +2257,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds175CvBennett</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -3118,38 +2265,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>175</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
         <v>2385.23847164413</v>
       </c>
-      <c r="K49" t="n">
+      <c r="G49" t="n">
         <v>1.13952527814804</v>
       </c>
-      <c r="L49" t="n">
+      <c r="H49" t="n">
         <v>578.75</v>
       </c>
-      <c r="M49" t="n">
+      <c r="I49" t="n">
         <v>15.4952949848226</v>
       </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
@@ -3158,10 +2291,6 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3169,36 +2298,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>250</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>374.646006308061</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.138319772313228</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>374.646006308061</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.138319772313228</v>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -3209,10 +2324,6 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3220,36 +2331,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>250</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>239.875</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.14232628300259</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>239.875</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.14232628300259</v>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -3260,10 +2357,6 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3271,34 +2364,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D52" t="n">
+        <v>0.72</v>
       </c>
       <c r="E52" t="n">
-        <v>250</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I52" t="n">
         <v>0.0168325082306035</v>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3311,10 +2390,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3322,34 +2397,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D53" t="n">
+        <v>0.8675</v>
       </c>
       <c r="E53" t="n">
-        <v>250</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>0.8675</v>
-      </c>
-      <c r="I53" t="n">
         <v>0.00629152869605898</v>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3362,10 +2423,6 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3373,50 +2430,32 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>250</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>886.25</v>
+      </c>
+      <c r="K54" t="n">
+        <v>33.4399337120555</v>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>886.25</v>
-      </c>
-      <c r="O54" t="n">
-        <v>33.4399337120555</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3424,34 +2463,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
+      <c r="D55" t="n">
+        <v>0.8075</v>
       </c>
       <c r="E55" t="n">
-        <v>250</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>0.8075</v>
-      </c>
-      <c r="I55" t="n">
         <v>0.00478713553878167</v>
       </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3464,10 +2489,6 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3475,7 +2496,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -3483,60 +2504,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>250</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>82.036</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.194629562673988</v>
+      </c>
+      <c r="N56" t="n">
+        <v>12.425</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.170171482138851</v>
+      </c>
       <c r="P56" t="n">
-        <v>82.036</v>
+        <v>10.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.194629562673988</v>
+        <v>0.433973885543051</v>
       </c>
       <c r="R56" t="n">
-        <v>12.425</v>
+        <v>1.02426871594756</v>
       </c>
       <c r="S56" t="n">
-        <v>0.170171482138851</v>
+        <v>0.0683584934502762</v>
       </c>
       <c r="T56" t="n">
-        <v>10.4</v>
+        <v>893.7830923597641</v>
       </c>
       <c r="U56" t="n">
-        <v>0.433973885543051</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.02426871594756</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0.0683584934502762</v>
-      </c>
-      <c r="X56" t="n">
-        <v>893.7830923597641</v>
-      </c>
-      <c r="Y56" t="n">
         <v>0.206018134737187</v>
       </c>
     </row>
@@ -3546,7 +2549,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -3554,38 +2557,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>GS16 30</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>250</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
         <v>2396.51309874161</v>
       </c>
-      <c r="K57" t="n">
+      <c r="G57" t="n">
         <v>1.50366840315618</v>
       </c>
-      <c r="L57" t="n">
+      <c r="H57" t="n">
         <v>566.25</v>
       </c>
-      <c r="M57" t="n">
+      <c r="I57" t="n">
         <v>35.2446804496792</v>
       </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
@@ -3594,10 +2583,6 @@
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3605,36 +2590,22 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>250</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>353.397712671764</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.212015574579103</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>353.397712671764</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.212015574579103</v>
-      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3645,10 +2616,6 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3656,36 +2623,22 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>250</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>255.875</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.100179526351446</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>255.875</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.100179526351446</v>
-      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -3696,10 +2649,6 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3707,34 +2656,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D60" t="n">
+        <v>0.7425</v>
       </c>
       <c r="E60" t="n">
-        <v>250</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>0.7425</v>
-      </c>
-      <c r="I60" t="n">
         <v>0.0239356776939085</v>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3747,10 +2682,6 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3758,34 +2689,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D61" t="n">
+        <v>0.87</v>
       </c>
       <c r="E61" t="n">
-        <v>250</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I61" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -3798,10 +2715,6 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3809,50 +2722,32 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>250</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>888.75</v>
+      </c>
+      <c r="K62" t="n">
+        <v>27.4146402493266</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>888.75</v>
-      </c>
-      <c r="O62" t="n">
-        <v>27.4146402493266</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3860,34 +2755,20 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
+      <c r="D63" t="n">
+        <v>0.8</v>
       </c>
       <c r="E63" t="n">
-        <v>250</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I63" t="n">
         <v>0.00707106781186547</v>
       </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -3900,10 +2781,6 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3911,7 +2788,7 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -3919,60 +2796,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>250</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>82.187</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.206018607573845</v>
+      </c>
+      <c r="N64" t="n">
+        <v>12.325</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.165201896679992</v>
+      </c>
       <c r="P64" t="n">
-        <v>82.187</v>
+        <v>10.875</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.206018607573845</v>
+        <v>0.213600093632938</v>
       </c>
       <c r="R64" t="n">
-        <v>12.325</v>
+        <v>1.17170400906137</v>
       </c>
       <c r="S64" t="n">
-        <v>0.165201896679992</v>
+        <v>0.111389709922316</v>
       </c>
       <c r="T64" t="n">
-        <v>10.875</v>
+        <v>859.617023890033</v>
       </c>
       <c r="U64" t="n">
-        <v>0.213600093632938</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.17170400906137</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0.111389709922316</v>
-      </c>
-      <c r="X64" t="n">
-        <v>859.617023890033</v>
-      </c>
-      <c r="Y64" t="n">
         <v>0.166009992609028</v>
       </c>
     </row>
@@ -3982,7 +2841,7 @@
           <t>FAR HYC W19-03-1GrazedGS16Seeds250CvBennett</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -3990,38 +2849,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>GS16</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>250</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="n">
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
         <v>2420.76227416057</v>
       </c>
-      <c r="K65" t="n">
+      <c r="G65" t="n">
         <v>1.65359341671253</v>
       </c>
-      <c r="L65" t="n">
+      <c r="H65" t="n">
         <v>554.375</v>
       </c>
-      <c r="M65" t="n">
+      <c r="I65" t="n">
         <v>56.1932584183073</v>
       </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
@@ -4030,10 +2875,6 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4041,36 +2882,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>43642</v>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>250</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>370.866567619304</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.158372305421424</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
-        <v>370.866567619304</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0.158372305421424</v>
-      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -4081,10 +2908,6 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4092,36 +2915,22 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>43677</v>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>250</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>230</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0445229341650645</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="n">
-        <v>230</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0.0445229341650645</v>
-      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -4132,10 +2941,6 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4143,34 +2948,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D68" t="n">
+        <v>0.67</v>
       </c>
       <c r="E68" t="n">
-        <v>250</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I68" t="n">
         <v>0.0108012344973464</v>
       </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
@@ -4183,10 +2974,6 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4194,34 +2981,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D69" t="n">
+        <v>0.8625</v>
       </c>
       <c r="E69" t="n">
-        <v>250</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="I69" t="n">
         <v>0.00853912563829967</v>
       </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
@@ -4234,10 +3007,6 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4245,50 +3014,32 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>43741</v>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>250</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>948.125</v>
+      </c>
+      <c r="K70" t="n">
+        <v>14.4832877828206</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
-        <v>948.125</v>
-      </c>
-      <c r="O70" t="n">
-        <v>14.4832877828206</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4296,34 +3047,20 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
+      <c r="D71" t="n">
+        <v>0.8175</v>
       </c>
       <c r="E71" t="n">
-        <v>250</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>0.8175</v>
-      </c>
-      <c r="I71" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -4336,10 +3073,6 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4347,7 +3080,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -4355,60 +3088,42 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>250</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>81.8305</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.17343274392878</v>
+      </c>
+      <c r="N72" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.108012344973465</v>
+      </c>
       <c r="P72" t="n">
-        <v>81.8305</v>
+        <v>10.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.17343274392878</v>
+        <v>0.285773803324704</v>
       </c>
       <c r="R72" t="n">
-        <v>12.2</v>
+        <v>1.35183018448932</v>
       </c>
       <c r="S72" t="n">
-        <v>0.108012344973465</v>
+        <v>0.145969731209932</v>
       </c>
       <c r="T72" t="n">
-        <v>10.5</v>
+        <v>847.2488157823281</v>
       </c>
       <c r="U72" t="n">
-        <v>0.285773803324704</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1.35183018448932</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0.145969731209932</v>
-      </c>
-      <c r="X72" t="n">
-        <v>847.2488157823281</v>
-      </c>
-      <c r="Y72" t="n">
         <v>0.248341424407127</v>
       </c>
     </row>
@@ -4418,7 +3133,7 @@
           <t>FAR HYC W19-03-1GrazedGS16 30 40NSeeds250CvBennett</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -4426,38 +3141,24 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>GS16 30 40N</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>250</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="n">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
         <v>2557.26628559363</v>
       </c>
-      <c r="K73" t="n">
+      <c r="G73" t="n">
         <v>0.899537494444816</v>
       </c>
-      <c r="L73" t="n">
+      <c r="H73" t="n">
         <v>569.375</v>
       </c>
-      <c r="M73" t="n">
+      <c r="I73" t="n">
         <v>27.6393250942686</v>
       </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
@@ -4466,10 +3167,6 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
